--- a/src/nodes/LPC/compressor_stage_2_blade_rotor_coordinates_lattice.xlsx
+++ b/src/nodes/LPC/compressor_stage_2_blade_rotor_coordinates_lattice.xlsx
@@ -346,10 +346,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>-21.606987817066774</v>
+        <v>-21.612852059519224</v>
       </c>
       <c r="B1">
-        <v>21.526564090917514</v>
+        <v>21.520676335575224</v>
       </c>
       <c r="C1">
         <v>374.58109848544609</v>
@@ -357,10 +357,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>-19.034522159449956</v>
+        <v>-19.2429252240448</v>
       </c>
       <c r="B2">
-        <v>21.276201264045572</v>
+        <v>21.132382117161487</v>
       </c>
       <c r="C2">
         <v>374.58109848544609</v>
@@ -368,10 +368,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>-17.129861581493916</v>
+        <v>-17.414734165619112</v>
       </c>
       <c r="B3">
-        <v>20.569164883483545</v>
+        <v>20.373409240154565</v>
       </c>
       <c r="C3">
         <v>374.58109848544609</v>
@@ -379,10 +379,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>-15.349686702843846</v>
+        <v>-15.693482845724093</v>
       </c>
       <c r="B4">
-        <v>19.77699988018847</v>
+        <v>19.541263645914896</v>
       </c>
       <c r="C4">
         <v>374.58109848544609</v>
@@ -390,10 +390,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>-13.662875395633112</v>
+        <v>-14.054078385787259</v>
       </c>
       <c r="B5">
-        <v>18.920988890612417</v>
+        <v>18.653114949157885</v>
       </c>
       <c r="C5">
         <v>374.58109848544609</v>
@@ -401,10 +401,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>-12.056249310464308</v>
+        <v>-12.485798849857886</v>
       </c>
       <c r="B6">
-        <v>18.010143831307619</v>
+        <v>17.716299554463276</v>
       </c>
       <c r="C6">
         <v>374.58109848544609</v>
@@ -412,10 +412,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>-10.522011040865237</v>
+        <v>-10.982247792896345</v>
       </c>
       <c r="B7">
-        <v>17.049796900892652</v>
+        <v>16.735194181566953</v>
       </c>
       <c r="C7">
         <v>374.58109848544609</v>
@@ -423,10 +423,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>-9.05530213052154</v>
+        <v>-9.53938937791934</v>
       </c>
       <c r="B8">
-        <v>16.043270518705274</v>
+        <v>15.712560321776401</v>
       </c>
       <c r="C8">
         <v>374.58109848544609</v>
@@ -434,10 +434,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>-7.6490420751843464</v>
+        <v>-8.1514309358228711</v>
       </c>
       <c r="B9">
-        <v>14.99540663509257</v>
+        <v>14.652361565653873</v>
       </c>
       <c r="C9">
         <v>374.58109848544609</v>
@@ -445,10 +445,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>-6.2956824246509706</v>
+        <v>-6.8122147617225117</v>
       </c>
       <c r="B10">
-        <v>13.911367201773544</v>
+        <v>13.558811276767502</v>
       </c>
       <c r="C10">
         <v>374.58109848544609</v>
@@ -456,10 +456,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-4.9880249928379587</v>
+        <v>-5.5158798397327553</v>
       </c>
       <c r="B11">
-        <v>12.796074644945556</v>
+        <v>12.435919811454223</v>
       </c>
       <c r="C11">
         <v>374.58109848544609</v>
@@ -467,10 +467,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-3.7220291197122881</v>
+        <v>-4.2590984372309837</v>
       </c>
       <c r="B12">
-        <v>11.652292140021212</v>
+        <v>11.285964145902367</v>
       </c>
       <c r="C12">
         <v>374.58109848544609</v>
@@ -478,10 +478,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-2.5059339853234306</v>
+        <v>-3.0483792656472013</v>
       </c>
       <c r="B13">
-        <v>10.474385384795758</v>
+        <v>10.104490742937072</v>
       </c>
       <c r="C13">
         <v>374.58109848544609</v>
@@ -489,10 +489,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-1.3445418853707531</v>
+        <v>-1.887489069444827</v>
       </c>
       <c r="B14">
-        <v>9.2590703649516932</v>
+        <v>8.88892223579742</v>
       </c>
       <c r="C14">
         <v>374.58109848544609</v>
@@ -500,10 +500,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-0.21662773807072222</v>
+        <v>-0.7593902811683364</v>
       </c>
       <c r="B15">
-        <v>8.0208616953379721</v>
+        <v>7.6509164527415132</v>
       </c>
       <c r="C15">
         <v>374.58109848544609</v>
@@ -511,10 +511,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>0.89727277747986456</v>
+        <v>0.35154065226963416</v>
       </c>
       <c r="B16">
-        <v>6.7730699075269891</v>
+        <v>6.40116369325896</v>
       </c>
       <c r="C16">
         <v>374.58109848544609</v>
@@ -522,10 +522,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>1.9835535611799844</v>
+        <v>1.434466914564821</v>
       </c>
       <c r="B17">
-        <v>5.5063905708184571</v>
+        <v>5.1322489467462971</v>
       </c>
       <c r="C17">
         <v>374.58109848544609</v>
@@ -533,10 +533,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>3.0245459186454449</v>
+        <v>2.4752954539231018</v>
       </c>
       <c r="B18">
-        <v>4.2087410795251179</v>
+        <v>3.8345291477907404</v>
       </c>
       <c r="C18">
         <v>374.58109848544609</v>
@@ -544,10 +544,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>4.0194011993636654</v>
+        <v>3.4733686459825561</v>
       </c>
       <c r="B19">
-        <v>2.8795410902844876</v>
+        <v>2.5075543218352148</v>
       </c>
       <c r="C19">
         <v>374.58109848544609</v>
@@ -555,10 +555,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>4.9714757637899742</v>
+        <v>4.4313877232393359</v>
       </c>
       <c r="B20">
-        <v>1.5210858253152515</v>
+        <v>1.1531727670365584</v>
       </c>
       <c r="C20">
         <v>374.58109848544609</v>
@@ -566,10 +566,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>5.8841259723796879</v>
+        <v>5.3520539181895721</v>
       </c>
       <c r="B21">
-        <v>0.13567050683611828</v>
+        <v>-0.2267672184483702</v>
       </c>
       <c r="C21">
         <v>374.58109848544609</v>
@@ -577,10 +577,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>6.7600985896676216</v>
+        <v>6.2375754457619363</v>
       </c>
       <c r="B22">
-        <v>-1.2748265105858998</v>
+        <v>-1.6307546800503614</v>
       </c>
       <c r="C22">
         <v>374.58109848544609</v>
@@ -588,10 +588,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>7.5997019965065356</v>
+        <v>7.0881884506151893</v>
       </c>
       <c r="B23">
-        <v>-2.7101943429904778</v>
+        <v>-3.0586280375506876</v>
       </c>
       <c r="C23">
         <v>374.58109848544609</v>
@@ -599,10 +599,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>8.4026349778286722</v>
+        <v>7.9036360598406228</v>
       </c>
       <c r="B24">
-        <v>-4.1706389740689653</v>
+        <v>-4.5105630543182436</v>
       </c>
       <c r="C24">
         <v>374.58109848544609</v>
@@ -610,10 +610,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>9.16859631856629</v>
+        <v>8.683661400529525</v>
       </c>
       <c r="B25">
-        <v>-5.6563663875127315</v>
+        <v>-5.986735493721949</v>
       </c>
       <c r="C25">
         <v>374.58109848544609</v>
@@ -621,10 +621,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>9.8971616049062039</v>
+        <v>9.4279035552872319</v>
       </c>
       <c r="B26">
-        <v>-7.167666815561982</v>
+        <v>-7.4873923107929761</v>
       </c>
       <c r="C26">
         <v>374.58109848544609</v>
@@ -632,10 +632,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>10.587413628053502</v>
+        <v>10.135585428775272</v>
       </c>
       <c r="B27">
-        <v>-8.705167484652419</v>
+        <v>-9.01306522721167</v>
       </c>
       <c r="C27">
         <v>374.58109848544609</v>
@@ -643,10 +643,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>11.238311980467847</v>
+        <v>10.805825881169191</v>
       </c>
       <c r="B28">
-        <v>-10.26957986976857</v>
+        <v>-10.56435715632063</v>
       </c>
       <c r="C28">
         <v>374.58109848544609</v>
@@ -654,10 +654,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>11.848816254608906</v>
+        <v>11.437743772644575</v>
       </c>
       <c r="B29">
-        <v>-11.861615445894998</v>
+        <v>-12.141871011462486</v>
       </c>
       <c r="C29">
         <v>374.58109848544609</v>
@@ -665,10 +665,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>12.418288572331257</v>
+        <v>12.030773522653206</v>
       </c>
       <c r="B30">
-        <v>-13.481710421273235</v>
+        <v>-13.745993786902364</v>
       </c>
       <c r="C30">
         <v>374.58109848544609</v>
@@ -676,10 +676,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>12.947701173069181</v>
+        <v>12.585611787751788</v>
       </c>
       <c r="B31">
-        <v>-15.129199937172755</v>
+        <v>-15.376248800595464</v>
       </c>
       <c r="C31">
         <v>374.58109848544609</v>
@@ -687,10 +687,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>13.438428825651894</v>
+        <v>13.103270783773269</v>
       </c>
       <c r="B32">
-        <v>-16.803143868120063</v>
+        <v>-17.031943451419529</v>
       </c>
       <c r="C32">
         <v>374.58109848544609</v>
@@ -698,10 +698,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>13.891846298908599</v>
+        <v>13.584762726550583</v>
       </c>
       <c r="B33">
-        <v>-18.50260208864163</v>
+        <v>-18.712385138252277</v>
       </c>
       <c r="C33">
         <v>374.58109848544609</v>
@@ -709,10 +709,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>14.30858373943008</v>
+        <v>14.030495564764873</v>
       </c>
       <c r="B34">
-        <v>-20.22714367766223</v>
+        <v>-20.417294725256074</v>
       </c>
       <c r="C34">
         <v>374.58109848544609</v>
@@ -720,10 +720,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>14.686292804853446</v>
+        <v>14.438460178490132</v>
       </c>
       <c r="B35">
-        <v>-21.9783745316999</v>
+        <v>-22.148046937731849</v>
       </c>
       <c r="C35">
         <v>374.58109848544609</v>
@@ -731,10 +731,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>15.021880530577375</v>
+        <v>14.80604318064856</v>
       </c>
       <c r="B36">
-        <v>-23.758409751670939</v>
+        <v>-23.906429966265154</v>
       </c>
       <c r="C36">
         <v>374.58109848544609</v>
@@ -742,10 +742,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>15.312253952000557</v>
+        <v>15.130631184162361</v>
       </c>
       <c r="B37">
-        <v>-25.569364438491718</v>
+        <v>-25.694232001441577</v>
       </c>
       <c r="C37">
         <v>374.58109848544609</v>
@@ -753,10 +753,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>15.552547155574189</v>
+        <v>15.408182170286036</v>
       </c>
       <c r="B38">
-        <v>-27.414566111074492</v>
+        <v>-27.514218764393195</v>
       </c>
       <c r="C38">
         <v>374.58109848544609</v>
@@ -764,10 +764,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>15.730802431959523</v>
+        <v>15.628939593603265</v>
       </c>
       <c r="B39">
-        <v>-29.302191960315273</v>
+        <v>-29.373066098438184</v>
       </c>
       <c r="C39">
         <v>374.58109848544609</v>
@@ -775,10 +775,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>15.833289122870333</v>
+        <v>15.78171827703002</v>
       </c>
       <c r="B40">
-        <v>-31.241631595106011</v>
+        <v>-31.278427377441222</v>
       </c>
       <c r="C40">
         <v>374.58109848544609</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>15.846276570020391</v>
+        <v>15.855333043482293</v>
       </c>
       <c r="B41">
-        <v>-33.24227462433867</v>
+        <v>-33.237955975266992</v>
       </c>
       <c r="C41">
         <v>374.58109848544609</v>
@@ -797,10 +797,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>15.846276570020391</v>
+        <v>15.855333043482293</v>
       </c>
       <c r="B42">
-        <v>-33.24227462433867</v>
+        <v>-33.237955975266992</v>
       </c>
       <c r="C42">
         <v>374.58109848544609</v>
@@ -808,10 +808,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>15.232354813024946</v>
+        <v>15.301060418471089</v>
       </c>
       <c r="B43">
-        <v>-31.65257606853049</v>
+        <v>-31.607313926569521</v>
       </c>
       <c r="C43">
         <v>374.58109848544609</v>
@@ -819,10 +819,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>14.632139527331484</v>
+        <v>14.750173062278872</v>
       </c>
       <c r="B44">
-        <v>-30.053504443920239</v>
+        <v>-29.974355532971156</v>
       </c>
       <c r="C44">
         <v>374.58109848544609</v>
@@ -830,10 +830,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>14.033927407139162</v>
+        <v>14.193512772501295</v>
       </c>
       <c r="B45">
-        <v>-28.453062969430288</v>
+        <v>-28.345347226053818</v>
       </c>
       <c r="C45">
         <v>374.58109848544609</v>
@@ -841,10 +841,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>13.426015146647131</v>
+        <v>13.621921346734036</v>
       </c>
       <c r="B46">
-        <v>-26.859254863983</v>
+        <v>-26.726555437399476</v>
       </c>
       <c r="C46">
         <v>374.58109848544609</v>
@@ -852,10 +852,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>12.798367001093213</v>
+        <v>13.027563845971116</v>
       </c>
       <c r="B47">
-        <v>-25.278942997245089</v>
+        <v>-25.123341165494708</v>
       </c>
       <c r="C47">
         <v>374.58109848544609</v>
@@ -863,10 +863,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>12.147617469869832</v>
+        <v>12.407898384799978</v>
       </c>
       <c r="B48">
-        <v>-23.714428841860627</v>
+        <v>-23.537443676444795</v>
       </c>
       <c r="C48">
         <v>374.58109848544609</v>
@@ -874,10 +874,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>11.472068613408064</v>
+        <v>11.761706341206397</v>
       </c>
       <c r="B49">
-        <v>-22.16687352121799</v>
+        <v>-21.96969680325963</v>
       </c>
       <c r="C49">
         <v>374.58109848544609</v>
@@ -885,10 +885,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>10.770022492138995</v>
+        <v>11.087769093176176</v>
       </c>
       <c r="B50">
-        <v>-20.637438158705596</v>
+        <v>-20.420934378949145</v>
       </c>
       <c r="C50">
         <v>374.58109848544609</v>
@@ -896,10 +896,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>10.040438968834351</v>
+        <v>10.385385482128376</v>
       </c>
       <c r="B51">
-        <v>-19.126834044457095</v>
+        <v>-18.891636166034584</v>
       </c>
       <c r="C51">
         <v>374.58109848544609</v>
@@ -907,10 +907,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>9.2849091156284409</v>
+        <v>9.65592420321513</v>
       </c>
       <c r="B52">
-        <v>-17.633973135587087</v>
+        <v>-17.380865645082473</v>
       </c>
       <c r="C52">
         <v>374.58109848544609</v>
@@ -918,10 +918,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>8.5056818069962166</v>
+        <v>8.90127141502185</v>
       </c>
       <c r="B53">
-        <v>-16.157317555955451</v>
+        <v>-15.887332226170656</v>
       </c>
       <c r="C53">
         <v>374.58109848544609</v>
@@ -929,10 +929,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>7.7050059174126222</v>
+        <v>8.1233132761339171</v>
       </c>
       <c r="B54">
-        <v>-14.695329429422014</v>
+        <v>-14.409745319376961</v>
       </c>
       <c r="C54">
         <v>374.58109848544609</v>
@@ -940,10 +940,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>6.8846637377282267</v>
+        <v>7.3235563435678337</v>
       </c>
       <c r="B55">
-        <v>-13.246789949599668</v>
+        <v>-12.947074074317087</v>
       </c>
       <c r="C55">
         <v>374.58109848544609</v>
@@ -951,10 +951,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>6.0445712242960568</v>
+        <v>6.5019887680644333</v>
       </c>
       <c r="B56">
-        <v>-11.811756589113445</v>
+        <v>-11.49932659875811</v>
       </c>
       <c r="C56">
         <v>374.58109848544609</v>
@@ -962,10 +962,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>5.1841777498447437</v>
+        <v>5.6582190987956293</v>
       </c>
       <c r="B57">
-        <v>-10.390605890341387</v>
+        <v>-10.066770740004928</v>
       </c>
       <c r="C57">
         <v>374.58109848544609</v>
@@ -973,10 +973,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>4.3029326871029312</v>
+        <v>4.7918558849333479</v>
       </c>
       <c r="B58">
-        <v>-8.9837143956615559</v>
+        <v>-8.64967434536247</v>
       </c>
       <c r="C58">
         <v>374.58109848544609</v>
@@ -984,10 +984,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>3.4003535587211555</v>
+        <v>3.9025566815705113</v>
       </c>
       <c r="B59">
-        <v>-7.5914120436330546</v>
+        <v>-7.2482717302002726</v>
       </c>
       <c r="C59">
         <v>374.58109848544609</v>
@@ -995,10 +995,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>2.4762304870375944</v>
+        <v>2.990175067484095</v>
       </c>
       <c r="B60">
-        <v>-6.2138423575392414</v>
+        <v>-5.8626630821464119</v>
       </c>
       <c r="C60">
         <v>374.58109848544609</v>
@@ -1006,10 +1006,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>1.5304217443123149</v>
+        <v>2.0546136273720736</v>
       </c>
       <c r="B61">
-        <v>-4.8511022568445092</v>
+        <v>-4.4929150568935761</v>
       </c>
       <c r="C61">
         <v>374.58109848544609</v>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>0.56278560280539514</v>
+        <v>1.0957749459324282</v>
       </c>
       <c r="B62">
-        <v>-3.5032886610132712</v>
+        <v>-3.1390943101344719</v>
       </c>
       <c r="C62">
         <v>374.58109848544609</v>
@@ -1028,10 +1028,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-0.42626439654352943</v>
+        <v>0.11400030831377268</v>
       </c>
       <c r="B63">
-        <v>-2.1701187731392944</v>
+        <v>-1.8009673200556235</v>
       </c>
       <c r="C63">
         <v>374.58109848544609</v>
@@ -1039,10 +1039,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-1.4340936380766156</v>
+        <v>-0.88861419853278056</v>
       </c>
       <c r="B64">
-        <v>-0.84979093083376178</v>
+        <v>-0.47709985481881828</v>
       </c>
       <c r="C64">
         <v>374.58109848544609</v>
@@ -1050,10 +1050,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-2.4575122374564495</v>
+        <v>-1.9095337872054707</v>
       </c>
       <c r="B65">
-        <v>0.45987624466276328</v>
+        <v>0.83424249492031677</v>
       </c>
       <c r="C65">
         <v>374.58109848544609</v>
@@ -1061,10 +1061,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-3.4933303103456339</v>
+        <v>-2.9462236703025568</v>
       </c>
       <c r="B66">
-        <v>1.7610641321097402</v>
+        <v>2.1347941385061748</v>
       </c>
       <c r="C66">
         <v>374.58109848544609</v>
@@ -1072,10 +1072,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-4.5426082419990577</v>
+        <v>-3.9995531674705975</v>
       </c>
       <c r="B67">
-        <v>3.0530475949105997</v>
+        <v>3.4239602504645461</v>
       </c>
       <c r="C67">
         <v>374.58109848544609</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-5.6234074960408131</v>
+        <v>-5.0840080265494105</v>
       </c>
       <c r="B68">
-        <v>4.3234754350447258</v>
+        <v>4.6918290660468669</v>
       </c>
       <c r="C68">
         <v>374.58109848544609</v>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-6.7497946117085332</v>
+        <v>-6.2108854171750894</v>
       </c>
       <c r="B69">
-        <v>5.5627283539212389</v>
+        <v>5.9306705813213059</v>
       </c>
       <c r="C69">
         <v>374.58109848544609</v>
@@ -1105,10 +1105,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-7.9028553523247753</v>
+        <v>-7.365111767975514</v>
       </c>
       <c r="B70">
-        <v>6.783740712092186</v>
+        <v>7.1507987748972575</v>
       </c>
       <c r="C70">
         <v>374.58109848544609</v>
@@ -1116,10 +1116,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>-9.061971412537444</v>
+        <v>-8.530256174851246</v>
       </c>
       <c r="B71">
-        <v>8.0006121848415468</v>
+        <v>8.3634563701632967</v>
       </c>
       <c r="C71">
         <v>374.58109848544609</v>
@@ -1127,10 +1127,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>-10.232688988210892</v>
+        <v>-9.7108291438017567</v>
       </c>
       <c r="B72">
-        <v>9.20955004723809</v>
+        <v>9.5655570870834836</v>
       </c>
       <c r="C72">
         <v>374.58109848544609</v>
@@ -1138,10 +1138,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>-11.424061453970921</v>
+        <v>-10.914153429104774</v>
       </c>
       <c r="B73">
-        <v>10.404363216151149</v>
+        <v>10.752090385745413</v>
       </c>
       <c r="C73">
         <v>374.58109848544609</v>
@@ -1149,10 +1149,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>-12.633006398272659</v>
+        <v>-12.137859368052185</v>
       </c>
       <c r="B74">
-        <v>11.587159575867638</v>
+        <v>11.924677690155363</v>
       </c>
       <c r="C74">
         <v>374.58109848544609</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>-13.853361229506502</v>
+        <v>-13.377121346244927</v>
       </c>
       <c r="B75">
-        <v>12.762153368980211</v>
+        <v>13.086620890917782</v>
       </c>
       <c r="C75">
         <v>374.58109848544609</v>
@@ -1171,10 +1171,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>-15.078778421974551</v>
+        <v>-14.626982359506004</v>
       </c>
       <c r="B76">
-        <v>13.933685303887</v>
+        <v>14.241311781111172</v>
       </c>
       <c r="C76">
         <v>374.58109848544609</v>
@@ -1182,10 +1182,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>-16.3034709253725</v>
+        <v>-15.882942951635378</v>
       </c>
       <c r="B77">
-        <v>15.105712812042693</v>
+        <v>15.391829080028755</v>
       </c>
       <c r="C77">
         <v>374.58109848544609</v>
@@ -1193,10 +1193,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>-17.524078525058673</v>
+        <v>-17.142465248118757</v>
       </c>
       <c r="B78">
-        <v>16.280533751322771</v>
+        <v>16.5399093093486</v>
       </c>
       <c r="C78">
         <v>374.58109848544609</v>
@@ -1204,10 +1204,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>-18.734400935446676</v>
+        <v>-18.400749627172132</v>
       </c>
       <c r="B79">
-        <v>17.462388141066484</v>
+        <v>17.6888365744225</v>
       </c>
       <c r="C79">
         <v>374.58109848544609</v>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>-19.923072355971982</v>
+        <v>-19.648886363901475</v>
       </c>
       <c r="B80">
-        <v>18.6590483997421</v>
+        <v>18.8447072879521</v>
       </c>
       <c r="C80">
         <v>374.58109848544609</v>
@@ -1226,10 +1226,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>-21.060969191914435</v>
+        <v>-20.86378074044573</v>
       </c>
       <c r="B81">
-        <v>19.890430481723346</v>
+        <v>20.023323838112642</v>
       </c>
       <c r="C81">
         <v>374.58109848544609</v>
@@ -1237,10 +1237,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>-21.606987817066774</v>
+        <v>-21.612852059519224</v>
       </c>
       <c r="B82">
-        <v>21.526564090917514</v>
+        <v>21.520676335575224</v>
       </c>
       <c r="C82">
         <v>374.58109848544609</v>
@@ -1258,10 +1258,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>-30.744268206493064</v>
+        <v>-30.426045861032041</v>
       </c>
       <c r="B1">
-        <v>16.450181570880336</v>
+        <v>17.031565827312726</v>
       </c>
       <c r="C1">
         <v>442.41419819725974</v>
@@ -1269,10 +1269,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>-28.644515022993318</v>
+        <v>-28.410042368566529</v>
       </c>
       <c r="B2">
-        <v>16.1727006481621</v>
+        <v>16.595050025999228</v>
       </c>
       <c r="C2">
         <v>442.41419819725974</v>
@@ -1280,10 +1280,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>-26.742012252683868</v>
+        <v>-26.548672827819743</v>
       </c>
       <c r="B3">
-        <v>15.5813605676949</v>
+        <v>15.922562670714614</v>
       </c>
       <c r="C3">
         <v>442.41419819725974</v>
@@ -1291,10 +1291,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>-24.874437063904963</v>
+        <v>-24.716526612581855</v>
       </c>
       <c r="B4">
-        <v>14.934444728758624</v>
+        <v>15.205480493556193</v>
       </c>
       <c r="C4">
         <v>442.41419819725974</v>
@@ -1302,10 +1302,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>-23.032741972044249</v>
+        <v>-22.906606027982026</v>
       </c>
       <c r="B5">
-        <v>14.24634922743369</v>
+        <v>14.454481983397448</v>
       </c>
       <c r="C5">
         <v>442.41419819725974</v>
@@ -1313,10 +1313,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>-21.21322427239804</v>
+        <v>-21.11604295146287</v>
       </c>
       <c r="B6">
-        <v>13.522965700451749</v>
+        <v>13.673943897925295</v>
       </c>
       <c r="C6">
         <v>442.41419819725974</v>
@@ -1324,10 +1324,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>-19.413761965106083</v>
+        <v>-19.34319104058682</v>
       </c>
       <c r="B7">
-        <v>12.767670612673433</v>
+        <v>12.866378557228831</v>
       </c>
       <c r="C7">
         <v>442.41419819725974</v>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>-17.633099091256998</v>
+        <v>-17.58707331441914</v>
       </c>
       <c r="B8">
-        <v>11.982462409626542</v>
+        <v>12.033276835122068</v>
       </c>
       <c r="C8">
         <v>442.41419819725974</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>-15.869286552231458</v>
+        <v>-15.846177975803805</v>
       </c>
       <c r="B9">
-        <v>11.170442440713268</v>
+        <v>11.176945735469476</v>
       </c>
       <c r="C9">
         <v>442.41419819725974</v>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>-14.120222595595777</v>
+        <v>-14.118875618431089</v>
       </c>
       <c r="B10">
-        <v>10.334954953674151</v>
+        <v>10.299871733813346</v>
       </c>
       <c r="C10">
         <v>442.41419819725974</v>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-12.383887993366761</v>
+        <v>-12.403601215597691</v>
       </c>
       <c r="B11">
-        <v>9.479212885728737</v>
+        <v>9.4044430623567621</v>
       </c>
       <c r="C11">
         <v>442.41419819725974</v>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-10.659198216983542</v>
+        <v>-10.699512147589779</v>
       </c>
       <c r="B12">
-        <v>8.60494190738469</v>
+        <v>8.4919455595657833</v>
       </c>
       <c r="C12">
         <v>442.41419819725974</v>
@@ -1390,10 +1390,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-8.9487250111241128</v>
+        <v>-9.0085910430450227</v>
       </c>
       <c r="B13">
-        <v>7.7080499328231609</v>
+        <v>7.5593537322975619</v>
       </c>
       <c r="C13">
         <v>442.41419819725974</v>
@@ -1401,10 +1401,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-7.2540021204751906</v>
+        <v>-7.3320189395086564</v>
       </c>
       <c r="B14">
-        <v>6.78609651181751</v>
+        <v>6.604865316160927</v>
       </c>
       <c r="C14">
         <v>442.41419819725974</v>
@@ -1412,10 +1412,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-5.5687550165195336</v>
+        <v>-5.6649452618047222</v>
       </c>
       <c r="B15">
-        <v>5.8490654928364867</v>
+        <v>5.6358822933803641</v>
       </c>
       <c r="C15">
         <v>442.41419819725974</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-3.8872287525003371</v>
+        <v>-4.0029211071122415</v>
       </c>
       <c r="B16">
-        <v>4.9061139808654346</v>
+        <v>4.6591936937935445</v>
       </c>
       <c r="C16">
         <v>442.41419819725974</v>
@@ -1434,10 +1434,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-2.2135549819063796</v>
+        <v>-2.3491358747512807</v>
       </c>
       <c r="B17">
-        <v>3.9506678082606475</v>
+        <v>3.6699324910752047</v>
       </c>
       <c r="C17">
         <v>442.41419819725974</v>
@@ -1445,10 +1445,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-0.55307257982926439</v>
+        <v>-0.70771195306459855</v>
       </c>
       <c r="B18">
-        <v>2.9742319112477449</v>
+        <v>2.6618079167847926</v>
       </c>
       <c r="C18">
         <v>442.41419819725974</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>1.0939372924738058</v>
+        <v>0.92113461565544053</v>
       </c>
       <c r="B19">
-        <v>1.9763589141586542</v>
+        <v>1.6344902901834613</v>
       </c>
       <c r="C19">
         <v>442.41419819725974</v>
@@ -1467,10 +1467,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>2.7284579022042226</v>
+        <v>2.5381643756290693</v>
       </c>
       <c r="B20">
-        <v>0.95861336335188507</v>
+        <v>0.58914020245779741</v>
       </c>
       <c r="C20">
         <v>442.41419819725974</v>
@@ -1478,10 +1478,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>4.351472516563379</v>
+        <v>4.1441378710765182</v>
       </c>
       <c r="B21">
-        <v>-0.077440194814053148</v>
+        <v>-0.47308175520561591</v>
       </c>
       <c r="C21">
         <v>442.41419819725974</v>
@@ -1489,10 +1489,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>5.9637889014011645</v>
+        <v>5.7396797609907741</v>
       </c>
       <c r="B22">
-        <v>-1.1305164666599021</v>
+        <v>-1.5512223526031961</v>
       </c>
       <c r="C22">
         <v>442.41419819725974</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>7.5655128171614647</v>
+        <v>7.3248711634558665</v>
       </c>
       <c r="B23">
-        <v>-2.2004471692234051</v>
+        <v>-2.6451578034633743</v>
       </c>
       <c r="C23">
         <v>442.41419819725974</v>
@@ -1511,10 +1511,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>9.15657452293664</v>
+        <v>8.89965731132856</v>
       </c>
       <c r="B24">
-        <v>-3.2873432722215417</v>
+        <v>-3.7549716824975734</v>
       </c>
       <c r="C24">
         <v>442.41419819725974</v>
@@ -1522,10 +1522,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>10.736904277819079</v>
+        <v>10.463983437465647</v>
       </c>
       <c r="B25">
-        <v>-4.3913157453713065</v>
+        <v>-4.8807475644172262</v>
       </c>
       <c r="C25">
         <v>442.41419819725974</v>
@@ -1533,10 +1533,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>12.306402567996813</v>
+        <v>12.017771481061912</v>
       </c>
       <c r="B26">
-        <v>-5.51252293217474</v>
+        <v>-6.022604570083586</v>
       </c>
       <c r="C26">
         <v>442.41419819725974</v>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>13.864850788040585</v>
+        <v>13.560850206664235</v>
       </c>
       <c r="B27">
-        <v>-6.6513126712741331</v>
+        <v>-7.1808040049572295</v>
       </c>
       <c r="C27">
         <v>442.41419819725974</v>
@@ -1555,10 +1555,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>15.412000559616763</v>
+        <v>15.093025085157469</v>
       </c>
       <c r="B28">
-        <v>-7.8080801750968085</v>
+        <v>-8.3556427206485324</v>
       </c>
       <c r="C28">
         <v>442.41419819725974</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>16.947603504391754</v>
+        <v>16.614101587426504</v>
       </c>
       <c r="B29">
-        <v>-8.98322065607011</v>
+        <v>-9.5474175687678962</v>
       </c>
       <c r="C29">
         <v>442.41419819725974</v>
@@ -1577,10 +1577,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>18.471540144526095</v>
+        <v>18.123984465609475</v>
       </c>
       <c r="B30">
-        <v>-10.176924223879745</v>
+        <v>-10.756273897640979</v>
       </c>
       <c r="C30">
         <v>442.41419819725974</v>
@@ -1588,10 +1588,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>19.984206604156977</v>
+        <v>19.622975596857632</v>
       </c>
       <c r="B31">
-        <v>-11.388560577244967</v>
+        <v>-11.981751042454533</v>
       </c>
       <c r="C31">
         <v>442.41419819725974</v>
@@ -1599,10 +1599,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>21.486127907915765</v>
+        <v>21.111476139575526</v>
       </c>
       <c r="B32">
-        <v>-12.617294312143409</v>
+        <v>-13.223236835110605</v>
       </c>
       <c r="C32">
         <v>442.41419819725974</v>
@@ -1610,10 +1610,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>22.977829080433803</v>
+        <v>22.589887252167671</v>
       </c>
       <c r="B33">
-        <v>-13.86229002455271</v>
+        <v>-14.480119107511225</v>
       </c>
       <c r="C33">
         <v>442.41419819725974</v>
@@ -1621,10 +1621,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>24.459624014054391</v>
+        <v>24.058446660924915</v>
       </c>
       <c r="B34">
-        <v>-15.123048258046365</v>
+        <v>-15.752035089115703</v>
       </c>
       <c r="C34">
         <v>442.41419819725974</v>
@@ -1632,10 +1632,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>25.930982071968707</v>
+        <v>25.516738363683434</v>
       </c>
       <c r="B35">
-        <v>-16.400413346581395</v>
+        <v>-17.039619599612493</v>
       </c>
       <c r="C35">
         <v>442.41419819725974</v>
@@ -1643,10 +1643,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>27.391161485079877</v>
+        <v>26.964182926165723</v>
       </c>
       <c r="B36">
-        <v>-17.695565571710677</v>
+        <v>-18.343756856247349</v>
       </c>
       <c r="C36">
         <v>442.41419819725974</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>28.839420484291033</v>
+        <v>28.400200914094274</v>
       </c>
       <c r="B37">
-        <v>-19.009685214987115</v>
+        <v>-19.665331076266</v>
       </c>
       <c r="C37">
         <v>442.41419819725974</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>30.27450124172907</v>
+        <v>29.823813912490802</v>
       </c>
       <c r="B38">
-        <v>-20.344773695776361</v>
+        <v>-21.005835321834223</v>
       </c>
       <c r="C38">
         <v>442.41419819725974</v>
@@ -1676,10 +1676,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>31.693081694415994</v>
+        <v>31.232447583573865</v>
       </c>
       <c r="B39">
-        <v>-21.706116984695161</v>
+        <v>-22.369198034797954</v>
       </c>
       <c r="C39">
         <v>442.41419819725974</v>
@@ -1687,10 +1687,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>33.091323720597572</v>
+        <v>32.623128608861244</v>
       </c>
       <c r="B40">
-        <v>-23.099822190173029</v>
+        <v>-23.759956501923146</v>
       </c>
       <c r="C40">
         <v>442.41419819725974</v>
@@ -1698,10 +1698,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>34.465389198519581</v>
+        <v>33.9928836698707</v>
       </c>
       <c r="B41">
-        <v>-24.531996420639484</v>
+        <v>-25.182648009975761</v>
       </c>
       <c r="C41">
         <v>442.41419819725974</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>34.465389198519581</v>
+        <v>33.9928836698707</v>
       </c>
       <c r="B42">
-        <v>-24.531996420639484</v>
+        <v>-25.182648009975761</v>
       </c>
       <c r="C42">
         <v>442.41419819725974</v>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>32.911457961709871</v>
+        <v>32.484173848893455</v>
       </c>
       <c r="B43">
-        <v>-23.386019388340163</v>
+        <v>-23.972001594717021</v>
       </c>
       <c r="C43">
         <v>442.41419819725974</v>
@@ -1731,10 +1731,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>31.36424069821204</v>
+        <v>30.978402444701064</v>
       </c>
       <c r="B44">
-        <v>-22.22935927571298</v>
+        <v>-22.756871152714925</v>
       </c>
       <c r="C44">
         <v>442.41419819725974</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>29.819962885308051</v>
+        <v>29.472661649807673</v>
       </c>
       <c r="B45">
-        <v>-21.068021994238819</v>
+        <v>-21.541694000894125</v>
       </c>
       <c r="C45">
         <v>442.41419819725974</v>
@@ -1753,10 +1753,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>28.274850000279852</v>
+        <v>27.964043656727409</v>
       </c>
       <c r="B46">
-        <v>-19.908013455398567</v>
+        <v>-20.330907456179283</v>
       </c>
       <c r="C46">
         <v>442.41419819725974</v>
@@ -1764,10 +1764,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>26.725641241310392</v>
+        <v>26.450037230517065</v>
       </c>
       <c r="B47">
-        <v>-18.754522152819881</v>
+        <v>-19.128343665426577</v>
       </c>
       <c r="C47">
         <v>442.41419819725974</v>
@@ -1775,10 +1775,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>25.171130690186544</v>
+        <v>24.929717426404025</v>
       </c>
       <c r="B48">
-        <v>-17.60946690871744</v>
+        <v>-17.935414095218235</v>
       </c>
       <c r="C48">
         <v>442.41419819725974</v>
@@ -1786,10 +1786,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>23.610626149596175</v>
+        <v>23.402555872158338</v>
       </c>
       <c r="B49">
-        <v>-16.473949127452663</v>
+        <v>-16.752925042068014</v>
       </c>
       <c r="C49">
         <v>442.41419819725974</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>22.043435422227148</v>
+        <v>21.868024195550039</v>
       </c>
       <c r="B50">
-        <v>-15.349070213386998</v>
+        <v>-15.581682802489663</v>
       </c>
       <c r="C50">
         <v>442.41419819725974</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>20.469074938438183</v>
+        <v>20.325754876550047</v>
       </c>
       <c r="B51">
-        <v>-14.235599608560491</v>
+        <v>-14.422248212388961</v>
       </c>
       <c r="C51">
         <v>442.41419819725974</v>
@@ -1819,10 +1819,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>18.887895639271413</v>
+        <v>18.776023803932794</v>
       </c>
       <c r="B52">
-        <v>-13.132978905727647</v>
+        <v>-13.274200265239857</v>
       </c>
       <c r="C52">
         <v>442.41419819725974</v>
@@ -1830,10 +1830,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>17.300457093439825</v>
+        <v>17.219267718673596</v>
       </c>
       <c r="B53">
-        <v>-12.040317735321585</v>
+        <v>-12.136872493908324</v>
       </c>
       <c r="C53">
         <v>442.41419819725974</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>15.707318869656401</v>
+        <v>15.655923361747728</v>
       </c>
       <c r="B54">
-        <v>-10.956725727775412</v>
+        <v>-11.009598431260327</v>
       </c>
       <c r="C54">
         <v>442.41419819725974</v>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>14.108909302750496</v>
+        <v>14.086325789339732</v>
       </c>
       <c r="B55">
-        <v>-9.88152132908574</v>
+        <v>-9.8918667812470229</v>
       </c>
       <c r="C55">
         <v>442.41419819725974</v>
@@ -1863,10 +1863,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>12.505131792017023</v>
+        <v>12.510403318471045</v>
       </c>
       <c r="B56">
-        <v>-8.8148582475031834</v>
+        <v>-8.7837869321603</v>
       </c>
       <c r="C56">
         <v>442.41419819725974</v>
@@ -1874,10 +1874,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>10.895758502867237</v>
+        <v>10.927982581372319</v>
       </c>
       <c r="B57">
-        <v>-7.7570990068418419</v>
+        <v>-7.6856234433772164</v>
       </c>
       <c r="C57">
         <v>442.41419819725974</v>
@@ -1885,10 +1885,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>9.2805616007124314</v>
+        <v>9.3388902102742328</v>
       </c>
       <c r="B58">
-        <v>-6.7086061309158351</v>
+        <v>-6.5976408742748456</v>
       </c>
       <c r="C58">
         <v>442.41419819725974</v>
@@ -1896,10 +1896,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>7.6593407506643709</v>
+        <v>7.7429737895268964</v>
       </c>
       <c r="B59">
-        <v>-5.669698386810432</v>
+        <v>-5.5200718112764688</v>
       </c>
       <c r="C59">
         <v>442.41419819725974</v>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>6.0320056166368863</v>
+        <v>6.1401647119583105</v>
       </c>
       <c r="B60">
-        <v>-4.6405195146956268</v>
+        <v>-4.4530209489903054</v>
       </c>
       <c r="C60">
         <v>442.41419819725974</v>
@@ -1918,10 +1918,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>4.3984933622442988</v>
+        <v>4.5304153225159309</v>
       </c>
       <c r="B61">
-        <v>-3.6211694980125797</v>
+        <v>-3.3965610090707892</v>
       </c>
       <c r="C61">
         <v>442.41419819725974</v>
@@ -1929,10 +1929,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>2.7587411511009532</v>
+        <v>2.9136779661472332</v>
       </c>
       <c r="B62">
-        <v>-2.6117483202024641</v>
+        <v>-2.3507647131723686</v>
       </c>
       <c r="C62">
         <v>442.41419819725974</v>
@@ -1940,10 +1940,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>1.1128593013075219</v>
+        <v>1.2900384556086062</v>
       </c>
       <c r="B63">
-        <v>-1.6120804462912128</v>
+        <v>-1.3155011109490669</v>
       </c>
       <c r="C63">
         <v>442.41419819725974</v>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-0.5383492510899226</v>
+        <v>-0.3398835251078306</v>
       </c>
       <c r="B64">
-        <v>-0.62088826764383831</v>
+        <v>-0.2898245640532498</v>
       </c>
       <c r="C64">
         <v>442.41419819725974</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-2.193908415558961</v>
+        <v>-1.9753348242010278</v>
       </c>
       <c r="B65">
-        <v>0.36338134278987438</v>
+        <v>0.7274142378631302</v>
       </c>
       <c r="C65">
         <v>442.41419819725974</v>
@@ -1973,10 +1973,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-3.8528421015671728</v>
+        <v>-3.6155622898699349</v>
       </c>
       <c r="B66">
-        <v>1.342281512060141</v>
+        <v>1.7373646051481226</v>
       </c>
       <c r="C66">
         <v>442.41419819725974</v>
@@ -1984,10 +1984,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-5.5154405417042938</v>
+        <v>-5.260791308448403</v>
       </c>
       <c r="B67">
-        <v>2.3153504304566979</v>
+        <v>2.7396825980469033</v>
       </c>
       <c r="C67">
         <v>442.41419819725974</v>
@@ -1995,10 +1995,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-7.1870592610486677</v>
+        <v>-6.9151614188098591</v>
       </c>
       <c r="B68">
-        <v>3.2740665412273473</v>
+        <v>3.7280512763931486</v>
       </c>
       <c r="C68">
         <v>442.41419819725974</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-8.8718493088853929</v>
+        <v>-8.58188199916113</v>
       </c>
       <c r="B69">
-        <v>4.2118248146977875</v>
+        <v>4.6975731260618874</v>
       </c>
       <c r="C69">
         <v>442.41419819725974</v>
@@ -2017,10 +2017,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-10.564078538837858</v>
+        <v>-10.256527632502946</v>
       </c>
       <c r="B70">
-        <v>5.1377460765471819</v>
+        <v>5.6550013375050145</v>
       </c>
       <c r="C70">
         <v>442.41419819725974</v>
@@ -2028,10 +2028,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>-12.257497327518053</v>
+        <v>-11.934273397504557</v>
       </c>
       <c r="B71">
-        <v>6.0617745469223374</v>
+        <v>6.6076987451554059</v>
       </c>
       <c r="C71">
         <v>442.41419819725974</v>
@@ -2039,10 +2039,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>-13.953669339153937</v>
+        <v>-13.616331150715316</v>
       </c>
       <c r="B72">
-        <v>6.9814221684871329</v>
+        <v>7.5538160547929882</v>
       </c>
       <c r="C72">
         <v>442.41419819725974</v>
@@ -2050,10 +2050,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>-15.655198666790239</v>
+        <v>-15.304716841619596</v>
       </c>
       <c r="B73">
-        <v>7.8925453836362847</v>
+        <v>8.4902769256318678</v>
       </c>
       <c r="C73">
         <v>442.41419819725974</v>
@@ -2061,10 +2061,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>-17.361037831122779</v>
+        <v>-16.998626013561779</v>
       </c>
       <c r="B74">
-        <v>8.796810911170807</v>
+        <v>9.4183089592758318</v>
       </c>
       <c r="C74">
         <v>442.41419819725974</v>
@@ -2072,10 +2072,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>-19.069207043304257</v>
+        <v>-18.696534264622258</v>
       </c>
       <c r="B75">
-        <v>9.6973689338968221</v>
+        <v>10.340238394470296</v>
       </c>
       <c r="C75">
         <v>442.41419819725974</v>
@@ -2083,10 +2083,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>-20.777648848663866</v>
+        <v>-20.396857817965543</v>
       </c>
       <c r="B76">
-        <v>10.597493214234612</v>
+        <v>11.258482076137499</v>
       </c>
       <c r="C76">
         <v>442.41419819725974</v>
@@ -2094,10 +2094,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>-22.484460955699213</v>
+        <v>-22.098133090701907</v>
       </c>
       <c r="B77">
-        <v>11.500210623454441</v>
+        <v>12.175273433126753</v>
       </c>
       <c r="C77">
         <v>442.41419819725974</v>
@@ -2105,10 +2105,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>-24.188439391405105</v>
+        <v>-23.799436650640676</v>
       </c>
       <c r="B78">
-        <v>12.407436888612335</v>
+        <v>13.092021623818855</v>
       </c>
       <c r="C78">
         <v>442.41419819725974</v>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>-25.887516503855334</v>
+        <v>-25.499178137125185</v>
       </c>
       <c r="B79">
-        <v>13.322461997706713</v>
+        <v>14.011153540053256</v>
       </c>
       <c r="C79">
         <v>442.41419819725974</v>
@@ -2127,10 +2127,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>-27.578048683710868</v>
+        <v>-27.194550299530256</v>
       </c>
       <c r="B80">
-        <v>14.25108355663264</v>
+        <v>14.936953048891803</v>
       </c>
       <c r="C80">
         <v>442.41419819725974</v>
@@ -2138,10 +2138,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>-29.251051257267811</v>
+        <v>-28.878620142160429</v>
       </c>
       <c r="B81">
-        <v>15.207597718567909</v>
+        <v>15.879999908206207</v>
       </c>
       <c r="C81">
         <v>442.41419819725974</v>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>-30.744268206493064</v>
+        <v>-30.426045861032041</v>
       </c>
       <c r="B82">
-        <v>16.450181570880336</v>
+        <v>17.031565827312726</v>
       </c>
       <c r="C82">
         <v>442.41419819725974</v>
@@ -2170,10 +2170,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>-36.316899591437931</v>
+        <v>-35.891805852305438</v>
       </c>
       <c r="B1">
-        <v>14.161410724790803</v>
+        <v>15.206611138291711</v>
       </c>
       <c r="C1">
         <v>501.14832753435888</v>
@@ -2181,10 +2181,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>-34.076769183159726</v>
+        <v>-33.727351300952591</v>
       </c>
       <c r="B2">
-        <v>13.909849902056536</v>
+        <v>14.745705255212952</v>
       </c>
       <c r="C2">
         <v>501.14832753435888</v>
@@ -2192,10 +2192,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>-31.958220833961541</v>
+        <v>-31.65064753100933</v>
       </c>
       <c r="B3">
-        <v>13.37663624458366</v>
+        <v>14.096678431034912</v>
       </c>
       <c r="C3">
         <v>501.14832753435888</v>
@@ -2203,10 +2203,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>-29.859721097835745</v>
+        <v>-29.589494156272409</v>
       </c>
       <c r="B4">
-        <v>12.796978656590506</v>
+        <v>13.414314525024766</v>
       </c>
       <c r="C4">
         <v>501.14832753435888</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>-27.775626005797964</v>
+        <v>-27.539876607509356</v>
       </c>
       <c r="B5">
-        <v>12.183951763360341</v>
+        <v>12.707220008030873</v>
       </c>
       <c r="C5">
         <v>501.14832753435888</v>
@@ -2225,10 +2225,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>-25.703634361383742</v>
+        <v>-25.500157384299168</v>
       </c>
       <c r="B6">
-        <v>11.542886437822958</v>
+        <v>11.978905368681362</v>
       </c>
       <c r="C6">
         <v>501.14832753435888</v>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>-23.642432632328379</v>
+        <v>-23.469401388381979</v>
       </c>
       <c r="B7">
-        <v>10.876825563843569</v>
+        <v>11.231375279320345</v>
       </c>
       <c r="C7">
         <v>501.14832753435888</v>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>-21.591248474424745</v>
+        <v>-21.447058397073079</v>
       </c>
       <c r="B8">
-        <v>10.187558327565078</v>
+        <v>10.465809312455338</v>
       </c>
       <c r="C8">
         <v>501.14832753435888</v>
@@ -2258,10 +2258,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>-19.548874561314697</v>
+        <v>-19.432268974542925</v>
       </c>
       <c r="B9">
-        <v>9.4778815798863931</v>
+        <v>9.6840499346088009</v>
       </c>
       <c r="C9">
         <v>501.14832753435888</v>
@@ -2269,10 +2269,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>-17.514007413474229</v>
+        <v>-17.424105359162873</v>
       </c>
       <c r="B10">
-        <v>8.7508149168378377</v>
+        <v>8.88808608978662</v>
       </c>
       <c r="C10">
         <v>501.14832753435888</v>
@@ -2280,10 +2280,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-15.485393920867026</v>
+        <v>-15.421675699252646</v>
       </c>
       <c r="B11">
-        <v>8.0092612502194012</v>
+        <v>8.0798297379134674</v>
       </c>
       <c r="C11">
         <v>501.14832753435888</v>
@@ -2291,10 +2291,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-13.462365112221326</v>
+        <v>-13.424503562529843</v>
       </c>
       <c r="B12">
-        <v>7.2547702959716736</v>
+        <v>7.260302258946262</v>
       </c>
       <c r="C12">
         <v>501.14832753435888</v>
@@ -2302,10 +2302,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-11.446538201836038</v>
+        <v>-11.433738284355133</v>
       </c>
       <c r="B13">
-        <v>6.4835956708279943</v>
+        <v>6.4270396970522068</v>
       </c>
       <c r="C13">
         <v>501.14832753435888</v>
@@ -2313,10 +2313,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-9.4388803950647873</v>
+        <v>-9.4500670347663789</v>
       </c>
       <c r="B14">
-        <v>5.6934967799860967</v>
+        <v>5.578568890714771</v>
       </c>
       <c r="C14">
         <v>501.14832753435888</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-7.4354726759094945</v>
+        <v>-7.4707025548671462</v>
       </c>
       <c r="B15">
-        <v>4.8935522817085291</v>
+        <v>4.7208651914722655</v>
       </c>
       <c r="C15">
         <v>501.14832753435888</v>
@@ -2335,10 +2335,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-5.4327205421640041</v>
+        <v>-5.49308838478763</v>
       </c>
       <c r="B16">
-        <v>4.0920890767197848</v>
+        <v>3.8594091617637454</v>
       </c>
       <c r="C16">
         <v>501.14832753435888</v>
@@ -2346,10 +2346,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-3.4332137681415444</v>
+        <v>-3.5190656896987913</v>
       </c>
       <c r="B17">
-        <v>3.2831077825272845</v>
+        <v>2.9902536945763902</v>
       </c>
       <c r="C17">
         <v>501.14832753435888</v>
@@ -2357,10 +2357,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-1.4402966729111424</v>
+        <v>-1.5510122364582339</v>
       </c>
       <c r="B18">
-        <v>2.458861064095021</v>
+        <v>2.1083013112122284</v>
       </c>
       <c r="C18">
         <v>501.14832753435888</v>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>0.54585252195442291</v>
+        <v>0.41094542637069076</v>
       </c>
       <c r="B19">
-        <v>1.6189360594303428</v>
+        <v>1.2132807156845036</v>
       </c>
       <c r="C19">
         <v>501.14832753435888</v>
@@ -2379,10 +2379,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>2.5258471192564542</v>
+        <v>2.3672435547982142</v>
       </c>
       <c r="B20">
-        <v>0.76475352480142733</v>
+        <v>0.30612715768425963</v>
       </c>
       <c r="C20">
         <v>501.14832753435888</v>
@@ -2390,10 +2390,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>4.5003004217962284</v>
+        <v>4.3183184048345424</v>
       </c>
       <c r="B21">
-        <v>-0.10226578352353863</v>
+        <v>-0.6122241130974494</v>
       </c>
       <c r="C21">
         <v>501.14832753435888</v>
@@ -2401,10 +2401,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>6.4697165382564386</v>
+        <v>6.2645285387372693</v>
       </c>
       <c r="B22">
-        <v>-0.9809540646324223</v>
+        <v>-1.5410044075588885</v>
       </c>
       <c r="C22">
         <v>501.14832753435888</v>
@@ -2412,10 +2412,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>8.43416280084532</v>
+        <v>8.20592174375342</v>
       </c>
       <c r="B23">
-        <v>-1.8711553390372644</v>
+        <v>-2.4801112789555391</v>
       </c>
       <c r="C23">
         <v>501.14832753435888</v>
@@ -2423,10 +2423,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>10.393597347652491</v>
+        <v>10.142468113377381</v>
       </c>
       <c r="B24">
-        <v>-2.7729665826061511</v>
+        <v>-3.4296088411321906</v>
       </c>
       <c r="C24">
         <v>501.14832753435888</v>
@@ -2434,10 +2434,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>12.3479783167676</v>
+        <v>12.074137741103559</v>
       </c>
       <c r="B25">
-        <v>-3.6864847712071755</v>
+        <v>-4.38956120793364</v>
       </c>
       <c r="C25">
         <v>501.14832753435888</v>
@@ -2445,10 +2445,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>14.297245803145644</v>
+        <v>14.000887844685051</v>
       </c>
       <c r="B26">
-        <v>-4.611848678816231</v>
+        <v>-5.360060096338561</v>
       </c>
       <c r="C26">
         <v>501.14832753435888</v>
@@ -2456,10 +2456,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>16.241267729203162</v>
+        <v>15.922624138909836</v>
       </c>
       <c r="B27">
-        <v>-5.5493642718404628</v>
+        <v>-6.3413076358611837</v>
       </c>
       <c r="C27">
         <v>501.14832753435888</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>18.179893974222061</v>
+        <v>17.839239462824583</v>
       </c>
       <c r="B28">
-        <v>-6.499379314794818</v>
+        <v>-7.3335335591496174</v>
       </c>
       <c r="C28">
         <v>501.14832753435888</v>
@@ -2478,10 +2478,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>20.112974417484256</v>
+        <v>19.750626655475994</v>
       </c>
       <c r="B29">
-        <v>-7.4622415721942517</v>
+        <v>-8.3369675988519738</v>
       </c>
       <c r="C29">
         <v>501.14832753435888</v>
@@ -2489,10 +2489,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>22.040440180381989</v>
+        <v>21.656736280180493</v>
       </c>
       <c r="B30">
-        <v>-8.4381106058629189</v>
+        <v>-9.3517157377901547</v>
       </c>
       <c r="C30">
         <v>501.14832753435888</v>
@@ -2500,10 +2500,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>23.962547352748718</v>
+        <v>23.557749797333486</v>
       </c>
       <c r="B31">
-        <v>-9.4263931668617751</v>
+        <v>-10.377388959481182</v>
       </c>
       <c r="C31">
         <v>501.14832753435888</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>25.879633266528323</v>
+        <v>25.45390639160021</v>
       </c>
       <c r="B32">
-        <v>-10.426307803561013</v>
+        <v>-11.413474497615901</v>
       </c>
       <c r="C32">
         <v>501.14832753435888</v>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>27.7920352536646</v>
+        <v>27.345445247645806</v>
       </c>
       <c r="B33">
-        <v>-11.437073064330788</v>
+        <v>-12.459459585885115</v>
       </c>
       <c r="C33">
         <v>501.14832753435888</v>
@@ -2533,10 +2533,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>29.699959208836212</v>
+        <v>29.232512039063305</v>
       </c>
       <c r="B34">
-        <v>-12.458211980608949</v>
+        <v>-13.515031927885636</v>
       </c>
       <c r="C34">
         <v>501.14832753435888</v>
@@ -2544,10 +2544,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>31.603085277661208</v>
+        <v>31.114878395157088</v>
       </c>
       <c r="B35">
-        <v>-13.490465516104024</v>
+        <v>-14.580681106838179</v>
       </c>
       <c r="C35">
         <v>501.14832753435888</v>
@@ -2555,10 +2555,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>33.500962168492428</v>
+        <v>32.992222434159331</v>
       </c>
       <c r="B36">
-        <v>-14.534879117592203</v>
+        <v>-15.657097175869431</v>
       </c>
       <c r="C36">
         <v>501.14832753435888</v>
@@ -2566,10 +2566,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>35.393138589682756</v>
+        <v>34.864222274302222</v>
       </c>
       <c r="B37">
-        <v>-15.592498231849683</v>
+        <v>-16.7449701881061</v>
       </c>
       <c r="C37">
         <v>501.14832753435888</v>
@@ -2577,10 +2577,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>37.278841008711076</v>
+        <v>36.730326849604893</v>
       </c>
       <c r="B38">
-        <v>-16.665114797826877</v>
+        <v>-17.845481523921862</v>
       </c>
       <c r="C38">
         <v>501.14832753435888</v>
@@ -2588,10 +2588,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>39.156006929560313</v>
+        <v>38.589068357234126</v>
       </c>
       <c r="B39">
-        <v>-17.757506723171044</v>
+        <v>-18.96177787267834</v>
       </c>
       <c r="C39">
         <v>501.14832753435888</v>
@@ -2599,10 +2599,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>41.022251615339371</v>
+        <v>40.438749810143577</v>
       </c>
       <c r="B40">
-        <v>-18.875198407703635</v>
+        <v>-20.097497250984112</v>
       </c>
       <c r="C40">
         <v>501.14832753435888</v>
@@ -2610,10 +2610,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>42.8751903291572</v>
+        <v>42.277674221286965</v>
       </c>
       <c r="B41">
-        <v>-20.023714251246105</v>
+        <v>-21.256277675447791</v>
       </c>
       <c r="C41">
         <v>501.14832753435888</v>
@@ -2621,10 +2621,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>42.8751903291572</v>
+        <v>42.277674221286965</v>
       </c>
       <c r="B42">
-        <v>-20.023714251246105</v>
+        <v>-21.256277675447791</v>
       </c>
       <c r="C42">
         <v>501.14832753435888</v>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>40.909725870958027</v>
+        <v>40.358734233993886</v>
       </c>
       <c r="B43">
-        <v>-19.135871693926095</v>
+        <v>-20.2690353871247</v>
       </c>
       <c r="C43">
         <v>501.14832753435888</v>
@@ -2643,10 +2643,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>38.950280847454522</v>
+        <v>38.4427792473134</v>
       </c>
       <c r="B44">
-        <v>-18.234084720313184</v>
+        <v>-19.275393826733591</v>
       </c>
       <c r="C44">
         <v>501.14832753435888</v>
@@ -2654,10 +2654,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>36.994477452120627</v>
+        <v>36.528119666336238</v>
       </c>
       <c r="B45">
-        <v>-17.323861675582524</v>
+        <v>-18.278975163550882</v>
       </c>
       <c r="C45">
         <v>501.14832753435888</v>
@@ -2665,10 +2665,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>35.039937878430351</v>
+        <v>34.613065896153188</v>
       </c>
       <c r="B46">
-        <v>-16.410710904909273</v>
+        <v>-17.283401566853005</v>
       </c>
       <c r="C46">
         <v>501.14832753435888</v>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>33.084606319029341</v>
+        <v>32.6961572682611</v>
       </c>
       <c r="B47">
-        <v>-15.499394821213576</v>
+        <v>-16.291804431358344</v>
       </c>
       <c r="C47">
         <v>501.14832753435888</v>
@@ -2687,10 +2687,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>31.127714963250163</v>
+        <v>30.776848819781396</v>
       </c>
       <c r="B48">
-        <v>-14.59169210839555</v>
+        <v>-15.305352053553152</v>
       </c>
       <c r="C48">
         <v>501.14832753435888</v>
@@ -2698,10 +2698,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>29.168817999597074</v>
+        <v>28.854824514241564</v>
       </c>
       <c r="B49">
-        <v>-13.688635518100305</v>
+        <v>-14.32472195536565</v>
       </c>
       <c r="C49">
         <v>501.14832753435888</v>
@@ -2709,10 +2709,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>27.207469616574365</v>
+        <v>26.929768315169174</v>
       </c>
       <c r="B50">
-        <v>-12.791257801972964</v>
+        <v>-13.350591658724071</v>
       </c>
       <c r="C50">
         <v>501.14832753435888</v>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>25.243355171278573</v>
+        <v>25.001457410589261</v>
       </c>
       <c r="B51">
-        <v>-11.900287850989372</v>
+        <v>-12.383438830012009</v>
       </c>
       <c r="C51">
         <v>501.14832753435888</v>
@@ -2731,10 +2731,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>23.276684695175327</v>
+        <v>23.070041886517011</v>
       </c>
       <c r="B52">
-        <v>-11.015239113448313</v>
+        <v>-11.422941713434573</v>
       </c>
       <c r="C52">
         <v>501.14832753435888</v>
@@ -2742,10 +2742,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>21.307799388322572</v>
+        <v>21.135765053465196</v>
       </c>
       <c r="B53">
-        <v>-10.135321176979327</v>
+        <v>-10.468578697652276</v>
       </c>
       <c r="C53">
         <v>501.14832753435888</v>
@@ -2753,10 +2753,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>19.337040450778176</v>
+        <v>19.198870221946489</v>
       </c>
       <c r="B54">
-        <v>-9.25974362921192</v>
+        <v>-9.5198281713255728</v>
       </c>
       <c r="C54">
         <v>501.14832753435888</v>
@@ -2764,10 +2764,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>17.364667582147948</v>
+        <v>17.2595427026487</v>
       </c>
       <c r="B55">
-        <v>-8.3879048589322256</v>
+        <v>-8.5762928636789866</v>
       </c>
       <c r="C55">
         <v>501.14832753435888</v>
@@ -2775,10 +2775,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>15.39061448022915</v>
+        <v>15.317735806959838</v>
       </c>
       <c r="B56">
-        <v>-7.5199584595527522</v>
+        <v>-7.6380728661930437</v>
       </c>
       <c r="C56">
         <v>501.14832753435888</v>
@@ -2786,10 +2786,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>13.41473334236688</v>
+        <v>13.373344846442929</v>
       </c>
       <c r="B57">
-        <v>-6.6562468256425991</v>
+        <v>-6.705392610912277</v>
       </c>
       <c r="C57">
         <v>501.14832753435888</v>
@@ -2797,10 +2797,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>11.436876365906265</v>
+        <v>11.426265132661037</v>
       </c>
       <c r="B58">
-        <v>-5.7971123517708767</v>
+        <v>-5.7784765298812291</v>
       </c>
       <c r="C58">
         <v>501.14832753435888</v>
@@ -2808,10 +2808,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>9.4569135353488534</v>
+        <v>9.4764045798844059</v>
       </c>
       <c r="B59">
-        <v>-4.9428562273891634</v>
+        <v>-4.8575220373435384</v>
       </c>
       <c r="C59">
         <v>501.14832753435888</v>
@@ -2819,10 +2819,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>7.4747859838219624</v>
+        <v>7.5237215132121458</v>
       </c>
       <c r="B60">
-        <v>-4.0936148214789689</v>
+        <v>-3.9426184763392556</v>
       </c>
       <c r="C60">
         <v>501.14832753435888</v>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>5.4904526316093287</v>
+        <v>5.5681868604505578</v>
       </c>
       <c r="B61">
-        <v>-3.2494832979042676</v>
+        <v>-3.033828172107524</v>
       </c>
       <c r="C61">
         <v>501.14832753435888</v>
@@ -2841,10 +2841,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>3.5038723989947052</v>
+        <v>3.609771549405957</v>
       </c>
       <c r="B62">
-        <v>-2.4105568205290453</v>
+        <v>-2.1312134498874968</v>
       </c>
       <c r="C62">
         <v>501.14832753435888</v>
@@ -2852,10 +2852,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>1.5151131345803772</v>
+        <v>1.6485239181268883</v>
       </c>
       <c r="B63">
-        <v>-1.5766782136045978</v>
+        <v>-1.2346706821212636</v>
       </c>
       <c r="C63">
         <v>501.14832753435888</v>
@@ -2863,10 +2863,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-0.47532159975725741</v>
+        <v>-0.31519805436919363</v>
       </c>
       <c r="B64">
-        <v>-0.74668094293146381</v>
+        <v>-0.34343243006265839</v>
       </c>
       <c r="C64">
         <v>501.14832753435888</v>
@@ -2874,10 +2874,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-2.4668193138232439</v>
+        <v>-2.2809589788225781</v>
       </c>
       <c r="B65">
-        <v>0.080853865302495651</v>
+        <v>0.54343469783153442</v>
       </c>
       <c r="C65">
         <v>501.14832753435888</v>
@@ -2885,10 +2885,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-4.4587675174226513</v>
+        <v>-4.2483234659735807</v>
       </c>
       <c r="B66">
-        <v>0.90734508490943033</v>
+        <v>1.4268640931045424</v>
       </c>
       <c r="C66">
         <v>501.14832753435888</v>
@@ -2896,10 +2896,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-6.4513454584552656</v>
+        <v>-6.2174191590969974</v>
       </c>
       <c r="B67">
-        <v>1.7323774763426558</v>
+        <v>2.306582112917007</v>
       </c>
       <c r="C67">
         <v>501.14832753435888</v>
@@ -2907,10 +2907,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-8.4478993371998037</v>
+        <v>-8.1906258316056189</v>
       </c>
       <c r="B68">
-        <v>2.5481993466201831</v>
+        <v>3.1774869768992571</v>
       </c>
       <c r="C68">
         <v>501.14832753435888</v>
@@ -2918,10 +2918,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-10.451021117662123</v>
+        <v>-10.169786984262828</v>
       </c>
       <c r="B69">
-        <v>3.3488062406825123</v>
+        <v>4.035626570973764</v>
       </c>
       <c r="C69">
         <v>501.14832753435888</v>
@@ -2929,10 +2929,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-12.457118866377641</v>
+        <v>-12.152348897096312</v>
       </c>
       <c r="B70">
-        <v>4.1425191085953612</v>
+        <v>4.8864755837618477</v>
       </c>
       <c r="C70">
         <v>501.14832753435888</v>
@@ -2940,10 +2940,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>-14.462276369756554</v>
+        <v>-14.135527300343115</v>
       </c>
       <c r="B71">
-        <v>4.9384101166582361</v>
+        <v>5.7360029586696824</v>
       </c>
       <c r="C71">
         <v>501.14832753435888</v>
@@ -2951,10 +2951,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>-16.467464191178614</v>
+        <v>-16.120012945813386</v>
       </c>
       <c r="B72">
-        <v>5.7342308909805446</v>
+        <v>6.5827278555440243</v>
       </c>
       <c r="C72">
         <v>501.14832753435888</v>
@@ -2962,10 +2962,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>-18.474303170080919</v>
+        <v>-18.106959035549906</v>
       </c>
       <c r="B73">
-        <v>6.5262266504245643</v>
+        <v>7.4241780291229693</v>
       </c>
       <c r="C73">
         <v>501.14832753435888</v>
@@ -2973,10 +2973,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>-20.482128473160504</v>
+        <v>-20.095893550952979</v>
       </c>
       <c r="B74">
-        <v>7.3159375250541459</v>
+        <v>8.2613653972694188</v>
       </c>
       <c r="C74">
         <v>501.14832753435888</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>-22.489691387158203</v>
+        <v>-22.085929330077931</v>
       </c>
       <c r="B75">
-        <v>8.1062562412458483</v>
+        <v>9.0961918660092884</v>
       </c>
       <c r="C75">
         <v>501.14832753435888</v>
@@ -2995,10 +2995,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>-24.49569335173026</v>
+        <v>-24.076143858242606</v>
       </c>
       <c r="B76">
-        <v>8.9001909994255133</v>
+        <v>9.9306351308957659</v>
       </c>
       <c r="C76">
         <v>501.14832753435888</v>
@@ -3006,10 +3006,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>-26.498932226624682</v>
+        <v>-26.065683231275248</v>
       </c>
       <c r="B77">
-        <v>9.7005266365360967</v>
+        <v>10.766525799631943</v>
       </c>
       <c r="C77">
         <v>501.14832753435888</v>
@@ -3017,10 +3017,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>-28.498641399041144</v>
+        <v>-28.054003339783083</v>
       </c>
       <c r="B78">
-        <v>10.509039061539754</v>
+        <v>11.60503033899322</v>
       </c>
       <c r="C78">
         <v>501.14832753435888</v>
@@ -3028,10 +3028,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>-30.493513314891469</v>
+        <v>-30.040175462010232</v>
       </c>
       <c r="B79">
-        <v>11.328757309462672</v>
+        <v>12.448139751315162</v>
       </c>
       <c r="C79">
         <v>501.14832753435888</v>
@@ -3039,10 +3039,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>-32.4812532460949</v>
+        <v>-32.02256899690947</v>
       </c>
       <c r="B80">
-        <v>12.164997268798555</v>
+        <v>13.29934973428427</v>
       </c>
       <c r="C80">
         <v>501.14832753435888</v>
@@ -3050,10 +3050,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>-34.456224070393731</v>
+        <v>-33.997176678174263</v>
       </c>
       <c r="B81">
-        <v>13.030817703937931</v>
+        <v>14.167251102668368</v>
       </c>
       <c r="C81">
         <v>501.14832753435888</v>
@@ -3061,10 +3061,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>-36.316899591437931</v>
+        <v>-35.891805852305438</v>
       </c>
       <c r="B82">
-        <v>14.161410724790803</v>
+        <v>15.206611138291711</v>
       </c>
       <c r="C82">
         <v>501.14832753435888</v>
